--- a/CORTES DE CAJA/2026/4) ABRIL/LISTA DE LAS VENTAS SEMANA 14 DE ABRIL-2026.xlsx
+++ b/CORTES DE CAJA/2026/4) ABRIL/LISTA DE LAS VENTAS SEMANA 14 DE ABRIL-2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBB3F9F2-F934-46F0-9C77-BD0BE96A1710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90573B6C-3F7B-421C-9077-6045A5A09B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1136,6 +1136,27 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1175,26 +1196,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1204,9 +1207,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1795,23 +1795,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -1824,14 +1824,14 @@
         <f>SUM(Tabla1[Importa])</f>
         <v>1691</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="31.5" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -1862,19 +1862,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>17</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -1893,21 +1893,21 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C36" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -1926,19 +1926,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -1960,19 +1960,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>171</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -1991,19 +1991,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>78</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -2025,19 +2025,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -2059,19 +2059,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -2093,19 +2093,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -2127,19 +2127,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -2161,19 +2161,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -2192,19 +2192,19 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>115</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -2223,17 +2223,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>500</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -2252,17 +2252,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -2284,17 +2284,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>262</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -2313,17 +2313,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -2342,17 +2342,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>68</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -2371,17 +2371,17 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -2400,12 +2400,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -2420,12 +2420,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -2454,14 +2454,14 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -2476,12 +2476,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -2496,18 +2496,18 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G26))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M26" s="31" t="s">
+      <c r="M26" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="31"/>
+      <c r="N26" s="38"/>
       <c r="O26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P26" s="31" t="s">
+      <c r="P26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -2522,12 +2522,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G27))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="27"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="34"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -2542,12 +2542,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G28))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="30"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="37"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -2562,12 +2562,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G29))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="23"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="27"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="34"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -2582,12 +2582,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G30))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="30"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="37"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -2602,12 +2602,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G31))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="27"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="34"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -2622,12 +2622,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G32))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="30"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="37"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -2642,12 +2642,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G33))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M33" s="19"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="27"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="34"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -2662,12 +2662,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G34))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="30"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="37"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -2682,12 +2682,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G35))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M35" s="19"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="27"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="34"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -2702,12 +2702,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G36))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M36" s="21"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="30"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="37"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -2722,12 +2722,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G37))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M37" s="19"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="27"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="34"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -2742,12 +2742,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G38))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="30"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="37"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -2762,12 +2762,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G39))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="23"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="27"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="34"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -2782,12 +2782,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G40))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M40" s="21"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="30"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="37"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -2802,12 +2802,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G41))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M41" s="19"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="27"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="32"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="34"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -2822,12 +2822,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G42))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M42" s="21"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="24"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="30"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="36"/>
+      <c r="R42" s="37"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -2842,12 +2842,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G43))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M43" s="19"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="23"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="27"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="34"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -2862,12 +2862,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G44))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M44" s="21"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="29"/>
-      <c r="R44" s="30"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="37"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -2882,12 +2882,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G45))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="26"/>
-      <c r="R45" s="27"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="34"/>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="18" t="str">
@@ -2902,12 +2902,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G46))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M46" s="21"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="30"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="37"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="18" t="str">
@@ -2922,12 +2922,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G47))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M47" s="19"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="25"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="27"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="34"/>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="str">
@@ -2942,12 +2942,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G48))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M48" s="21"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="30"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="37"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="str">
@@ -2962,12 +2962,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G49))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M49" s="19"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="25"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="27"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="34"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="18" t="str">
@@ -2982,12 +2982,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G50))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M50" s="21"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="30"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="37"/>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="18" t="str">
@@ -3002,12 +3002,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G51))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20"/>
-      <c r="O51" s="23"/>
-      <c r="P51" s="25"/>
-      <c r="Q51" s="26"/>
-      <c r="R51" s="27"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="34"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="18" t="str">
@@ -3022,12 +3022,12 @@
         <f>IF(Tabla1[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla1[[#This Row],[Cantidad]]*Tabla1[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G52))), ( Tabla1[[#This Row],[Cantidad]]* Tabla1[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla1[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M52" s="21"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="30"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="37"/>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="18" t="str">
@@ -3746,19 +3746,33 @@
   </sheetData>
   <autoFilter ref="B4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="48">
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M41:N42"/>
-    <mergeCell ref="M43:N44"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P41:R42"/>
-    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:R50"/>
+    <mergeCell ref="M51:N52"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M45:N46"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="P45:R46"/>
+    <mergeCell ref="M47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:R48"/>
+    <mergeCell ref="P31:R32"/>
+    <mergeCell ref="P33:R34"/>
+    <mergeCell ref="P35:R36"/>
+    <mergeCell ref="P37:R38"/>
+    <mergeCell ref="P39:R40"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="M31:N32"/>
+    <mergeCell ref="M33:N34"/>
+    <mergeCell ref="M35:N36"/>
+    <mergeCell ref="M37:N38"/>
+    <mergeCell ref="M39:N40"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="M27:N28"/>
@@ -3767,33 +3781,19 @@
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="P27:R28"/>
     <mergeCell ref="P29:R30"/>
-    <mergeCell ref="M31:N32"/>
-    <mergeCell ref="M33:N34"/>
-    <mergeCell ref="M35:N36"/>
-    <mergeCell ref="M37:N38"/>
-    <mergeCell ref="M39:N40"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="P31:R32"/>
-    <mergeCell ref="P33:R34"/>
-    <mergeCell ref="P35:R36"/>
-    <mergeCell ref="P37:R38"/>
-    <mergeCell ref="P39:R40"/>
-    <mergeCell ref="M45:N46"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="P45:R46"/>
-    <mergeCell ref="M47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:R48"/>
-    <mergeCell ref="M49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:R50"/>
-    <mergeCell ref="M51:N52"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="P51:R52"/>
+    <mergeCell ref="M41:N42"/>
+    <mergeCell ref="M43:N44"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P41:R42"/>
+    <mergeCell ref="P43:R44"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -3833,23 +3833,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -3862,14 +3862,14 @@
         <f>SUM(Tabla110[Importa])</f>
         <v>2517</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -3900,19 +3900,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>21</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla110[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -3931,21 +3931,21 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>121</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -3967,19 +3967,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>360</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -4001,19 +4001,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -4035,19 +4035,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -4069,19 +4069,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -4103,19 +4103,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>65</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -4137,19 +4137,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -4168,19 +4168,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>15</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -4202,19 +4202,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -4236,19 +4236,19 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -4270,17 +4270,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -4302,17 +4302,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -4334,17 +4334,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>125.5</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -4366,17 +4366,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>67.5</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -4398,17 +4398,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -4427,17 +4427,17 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>750</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -4459,12 +4459,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -4488,12 +4488,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -4540,14 +4540,14 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -4571,12 +4571,12 @@
         <f>IF(Tabla110[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla110[[#This Row],[Cantidad]]*Tabla110[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla110[[#This Row],[Cantidad]]* Tabla110[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla110[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>156</v>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -4597,12 +4597,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -4623,10 +4623,10 @@
       <c r="N27" s="15">
         <v>3851</v>
       </c>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -4647,10 +4647,10 @@
       <c r="N28" s="15">
         <v>930</v>
       </c>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -4671,10 +4671,10 @@
       <c r="N29" s="15">
         <v>4781</v>
       </c>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -4691,10 +4691,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -4711,10 +4711,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -4731,10 +4731,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -4751,10 +4751,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -4771,10 +4771,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -4791,10 +4791,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -4811,10 +4811,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -4831,10 +4831,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -4851,10 +4851,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -4871,10 +4871,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -4891,10 +4891,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -4911,10 +4911,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -4931,10 +4931,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -4951,10 +4951,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -4971,10 +4971,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -5804,32 +5804,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="11" priority="1">
@@ -5867,23 +5867,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -5896,14 +5896,14 @@
         <f>SUM(Tabla111[Importa])</f>
         <v>629.5</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -5934,17 +5934,17 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>14</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla111[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f>IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -5966,21 +5966,21 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6" si="0">IF(ISNUMBER(E6), IF(ISNUMBER(C5), C5+1, 1), "")</f>
@@ -6002,19 +6002,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f>IF(ISNUMBER(E7), IF(ISNUMBER(C6), C6+1, 1), "")</f>
@@ -6036,19 +6036,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" ref="C8:C68" si="1">IF(ISNUMBER(E8), IF(ISNUMBER(C7), C7+1, 1), "")</f>
@@ -6070,19 +6070,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="1"/>
@@ -6104,19 +6104,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>28</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="1"/>
@@ -6138,19 +6138,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="1"/>
@@ -6169,19 +6169,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>115</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="1"/>
@@ -6200,19 +6200,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>5</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
@@ -6234,19 +6234,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
@@ -6265,19 +6265,19 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>89</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
@@ -6296,17 +6296,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>10</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
@@ -6325,17 +6325,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
@@ -6354,17 +6354,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>30</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
@@ -6383,17 +6383,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="1"/>
@@ -6403,17 +6403,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="1"/>
@@ -6423,17 +6423,17 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="1"/>
@@ -6443,12 +6443,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -6463,12 +6463,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -6497,14 +6497,14 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -6519,12 +6519,12 @@
         <f>IF(Tabla111[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla111[[#This Row],[Cantidad]]*Tabla111[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla111[[#This Row],[Cantidad]]* Tabla111[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla111[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -6545,12 +6545,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -6567,10 +6567,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -6587,10 +6587,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -6607,10 +6607,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -6627,10 +6627,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -6647,10 +6647,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -6667,10 +6667,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -6687,10 +6687,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -6707,10 +6707,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -6727,10 +6727,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -6747,10 +6747,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -6767,10 +6767,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -6787,10 +6787,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -6807,10 +6807,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -6827,10 +6827,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -6847,10 +6847,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -6867,10 +6867,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -6887,10 +6887,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -6907,10 +6907,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -7740,32 +7740,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="9" priority="1">
@@ -7804,23 +7804,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -7833,14 +7833,14 @@
         <f>SUM(Tabla112[Importa])</f>
         <v>1078.5</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -7871,19 +7871,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>11</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla112[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -7902,21 +7902,21 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>35</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -7935,19 +7935,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -7966,19 +7966,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>50</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -7997,19 +7997,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -8028,19 +8028,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>117</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -8059,19 +8059,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>110</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -8093,19 +8093,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>450</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -8127,19 +8127,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>53.5</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -8158,19 +8158,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>20</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -8189,19 +8189,19 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>78</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -8220,17 +8220,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -8240,17 +8240,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -8260,17 +8260,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -8280,17 +8280,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -8300,17 +8300,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -8320,17 +8320,17 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -8340,12 +8340,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -8360,12 +8360,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -8394,14 +8394,14 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -8416,12 +8416,12 @@
         <f>IF(Tabla112[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla112[[#This Row],[Cantidad]]*Tabla112[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla112[[#This Row],[Cantidad]]* Tabla112[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla112[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -8442,12 +8442,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -8468,10 +8468,10 @@
       <c r="N27" s="15">
         <v>8940</v>
       </c>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -8492,10 +8492,10 @@
       <c r="N28" s="15">
         <v>100</v>
       </c>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -8512,10 +8512,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -8532,10 +8532,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -8552,10 +8552,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -8572,10 +8572,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -8592,10 +8592,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -8612,10 +8612,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -8632,10 +8632,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -8652,10 +8652,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -8672,10 +8672,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -8692,10 +8692,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -8712,10 +8712,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -8732,10 +8732,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -8752,10 +8752,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -8792,10 +8792,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -8812,10 +8812,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -9645,32 +9645,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="7" priority="1">
@@ -9709,23 +9709,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -9738,14 +9738,14 @@
         <f>SUM(Tabla113[Importa])</f>
         <v>1966.5</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -9776,19 +9776,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>18</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla113[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -9807,21 +9807,21 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -9840,19 +9840,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -9871,19 +9871,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>12</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -9902,19 +9902,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>250</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -9933,19 +9933,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>67</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -9967,19 +9967,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -9998,19 +9998,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>750</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -10032,19 +10032,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>45</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -10066,19 +10066,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>130.5</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -10097,19 +10097,19 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -10128,17 +10128,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>100</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -10160,17 +10160,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>13.5</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -10192,17 +10192,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>38</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -10224,17 +10224,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>89.5</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -10253,17 +10253,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>53</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -10285,17 +10285,17 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>31</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -10317,12 +10317,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>9</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -10349,12 +10349,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>63</v>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -10383,14 +10383,14 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -10405,12 +10405,12 @@
         <f>IF(Tabla113[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla113[[#This Row],[Cantidad]]*Tabla113[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla113[[#This Row],[Cantidad]]* Tabla113[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla113[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -10431,12 +10431,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -10457,12 +10457,12 @@
       <c r="N27" s="15">
         <v>3851</v>
       </c>
-      <c r="O27" s="39" t="s">
+      <c r="O27" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -10483,12 +10483,12 @@
       <c r="N28" s="15">
         <v>930</v>
       </c>
-      <c r="O28" s="39" t="s">
+      <c r="O28" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -10509,12 +10509,12 @@
       <c r="N29" s="15">
         <v>8940</v>
       </c>
-      <c r="O29" s="39" t="s">
+      <c r="O29" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -10535,12 +10535,12 @@
       <c r="N30" s="15">
         <v>100</v>
       </c>
-      <c r="O30" s="39" t="s">
+      <c r="O30" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -10561,12 +10561,12 @@
       <c r="N31" s="15">
         <v>1500</v>
       </c>
-      <c r="O31" s="39" t="s">
+      <c r="O31" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -10587,12 +10587,12 @@
       <c r="N32" s="15">
         <v>15321</v>
       </c>
-      <c r="O32" s="39" t="s">
+      <c r="O32" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -10609,10 +10609,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -10629,10 +10629,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -10649,10 +10649,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -10669,10 +10669,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -10689,10 +10689,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -10709,10 +10709,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -10729,10 +10729,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -10749,10 +10749,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -10769,10 +10769,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -10789,10 +10789,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -10809,10 +10809,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -10829,10 +10829,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -11662,32 +11662,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -11725,23 +11725,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -11754,14 +11754,14 @@
         <f>SUM(Tabla114[Importa])</f>
         <v>3087</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -11792,19 +11792,19 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>23</v>
       </c>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <f ca="1">IF(Tabla114[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C68" si="0">IF(ISNUMBER(E5), IF(ISNUMBER(C4), C4+1, 1), "")</f>
@@ -11826,21 +11826,21 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -11862,19 +11862,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>189</v>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -11896,19 +11896,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>94.5</v>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -11930,19 +11930,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>166.5</v>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -11964,19 +11964,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>239.5</v>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -11998,19 +11998,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>146</v>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -12032,19 +12032,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>58.5</v>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -12063,19 +12063,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>42</v>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -12094,19 +12094,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>250</v>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -12128,19 +12128,19 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>135</v>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -12162,17 +12162,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>111.5</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -12194,17 +12194,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>27</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -12226,17 +12226,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>54</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
@@ -12258,17 +12258,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>90</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
@@ -12287,17 +12287,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>115</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -12316,17 +12316,17 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>690</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
@@ -12345,12 +12345,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>192</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -12374,12 +12374,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>52</v>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -12426,14 +12426,14 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>30</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -12457,12 +12457,12 @@
         <f>IF(Tabla114[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla114[[#This Row],[Cantidad]]*Tabla114[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla114[[#This Row],[Cantidad]]* Tabla114[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla114[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v>78</v>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -12495,12 +12495,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -12529,10 +12529,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -12549,10 +12549,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -12569,10 +12569,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -12589,10 +12589,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -12609,10 +12609,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -12629,10 +12629,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -12649,10 +12649,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -12669,10 +12669,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -12689,10 +12689,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -12709,10 +12709,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -12729,10 +12729,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -12749,10 +12749,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -12769,10 +12769,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -12789,10 +12789,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -12809,10 +12809,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -12829,10 +12829,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -12849,10 +12849,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -12869,10 +12869,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -13702,32 +13702,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -13765,23 +13765,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="2:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="G3" t="s">
@@ -13794,14 +13794,14 @@
         <f>SUM(Tabla115[Importa])</f>
         <v>0</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
     </row>
     <row r="4" spans="2:18" ht="33.75" x14ac:dyDescent="0.5">
       <c r="B4" s="17" t="s">
@@ -13832,12 +13832,12 @@
         <f>COUNTIF(C5:C103,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="str">
@@ -13852,21 +13852,21 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G5))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
+      <c r="K5" s="25"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
     </row>
     <row r="6" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -13876,19 +13876,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G6))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -13898,19 +13898,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G7))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -13920,19 +13920,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G8))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -13942,19 +13942,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G9))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -13964,19 +13964,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G10))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -13986,19 +13986,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G11))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -14008,19 +14008,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G12))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -14030,19 +14030,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G13))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="36"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -14052,19 +14052,19 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G14))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -14074,17 +14074,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G15))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="36"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -14094,17 +14094,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G16))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -14114,17 +14114,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G17))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -14134,17 +14134,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G18))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -14154,17 +14154,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G19))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -14174,17 +14174,17 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G20))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <f ca="1">IF(Tabla1[[#This Row],['#]]&lt;&gt;"", NOW(), "")</f>
-        <v>46123.797432175925</v>
+        <v>46125.78946550926</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -14194,12 +14194,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G21))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="str">
@@ -14214,12 +14214,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G22))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="str">
@@ -14248,14 +14248,14 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G24))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="str">
@@ -14270,12 +14270,12 @@
         <f>IF(Tabla115[[#This Row],[Cantidad]] &gt; 0,CEILING(( Tabla115[[#This Row],[Cantidad]]*Tabla115[[#This Row],[Precio]]) - IF(ISNUMBER(FIND("x", LOWER(G25))), ( Tabla115[[#This Row],[Cantidad]]* Tabla115[[#This Row],[Precio]] * IF(ISNUMBER(FIND("aceite", LOWER(Tabla115[[#This Row],[Producto]]))), 0.05, 0.1)), 0), 0.5), "")</f>
         <v/>
       </c>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="str">
@@ -14296,12 +14296,12 @@
       <c r="N26" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
     </row>
     <row r="27" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="str">
@@ -14318,10 +14318,10 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="40"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="41"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="str">
@@ -14338,10 +14338,10 @@
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="41"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="str">
@@ -14358,10 +14358,10 @@
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="41"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="str">
@@ -14378,10 +14378,10 @@
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="40"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="str">
@@ -14398,10 +14398,10 @@
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="str">
@@ -14418,10 +14418,10 @@
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="40"/>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="41"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="str">
@@ -14438,10 +14438,10 @@
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="15"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="41"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="str">
@@ -14458,10 +14458,10 @@
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="str">
@@ -14478,10 +14478,10 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="15"/>
-      <c r="O35" s="39"/>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="str">
@@ -14498,10 +14498,10 @@
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="15"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="18" t="str">
@@ -14518,10 +14518,10 @@
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="15"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="41"/>
+      <c r="Q37" s="41"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="str">
@@ -14538,10 +14538,10 @@
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="15"/>
-      <c r="O38" s="39"/>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="42"/>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="str">
@@ -14558,10 +14558,10 @@
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-      <c r="R39" s="41"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="41"/>
+      <c r="Q39" s="41"/>
+      <c r="R39" s="42"/>
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="str">
@@ -14578,10 +14578,10 @@
       </c>
       <c r="M40" s="13"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="41"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="42"/>
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="str">
@@ -14598,10 +14598,10 @@
       </c>
       <c r="M41" s="13"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="42"/>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="str">
@@ -14618,10 +14618,10 @@
       </c>
       <c r="M42" s="13"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="41"/>
+      <c r="O42" s="40"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="42"/>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="str">
@@ -14638,10 +14638,10 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="41"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="41"/>
+      <c r="Q43" s="41"/>
+      <c r="R43" s="42"/>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="str">
@@ -14658,10 +14658,10 @@
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="15"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="41"/>
+      <c r="O44" s="40"/>
+      <c r="P44" s="41"/>
+      <c r="Q44" s="41"/>
+      <c r="R44" s="42"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="18" t="str">
@@ -15491,32 +15491,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="M3:R3"/>
-    <mergeCell ref="M4:R22"/>
-    <mergeCell ref="J5:K14"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="M25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O31:R31"/>
-    <mergeCell ref="O32:R32"/>
-    <mergeCell ref="O33:R33"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O38:R38"/>
     <mergeCell ref="O44:R44"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="O40:R40"/>
     <mergeCell ref="O41:R41"/>
     <mergeCell ref="O42:R42"/>
     <mergeCell ref="O43:R43"/>
+    <mergeCell ref="O34:R34"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O30:R30"/>
+    <mergeCell ref="O31:R31"/>
+    <mergeCell ref="O32:R32"/>
+    <mergeCell ref="O33:R33"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="M25:R25"/>
+    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="M3:R3"/>
+    <mergeCell ref="M4:R22"/>
+    <mergeCell ref="J5:K14"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B103">
     <cfRule type="expression" dxfId="1" priority="1">
